--- a/data/trans_orig/P36B07-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36B07-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de zumo natural de frutas o verduras en 2016</t>
+          <t>Población según la frecuencia de consumo de zumo natural de frutas o verduras en 2016 (tasa de respuesta: 99,24%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>225100</t>
+          <t>222333</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>275170</t>
+          <t>272175</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>263708</t>
+          <t>260610</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>321862</t>
+          <t>320143</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>500808</t>
+          <t>501007</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>578007</t>
+          <t>578890</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,34%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>109979</t>
+          <t>107998</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>151281</t>
+          <t>148086</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>145890</t>
+          <t>144451</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>197927</t>
+          <t>194776</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>264848</t>
+          <t>266345</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>328641</t>
+          <t>331222</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,07%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>117239</t>
+          <t>120165</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>159231</t>
+          <t>159754</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>164237</t>
+          <t>166374</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>219561</t>
+          <t>218591</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>302679</t>
+          <t>298632</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>369404</t>
+          <t>365622</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,06%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>116110</t>
+          <t>117115</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>157805</t>
+          <t>158157</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>164967</t>
+          <t>165273</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>215886</t>
+          <t>217021</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>293811</t>
+          <t>291920</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>360928</t>
+          <t>358483</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,64%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>84721</t>
+          <t>84143</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>121337</t>
+          <t>122946</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>120227</t>
+          <t>121114</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>165648</t>
+          <t>166330</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>215065</t>
+          <t>214289</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>274278</t>
+          <t>271612</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>445011</t>
+          <t>442411</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>519388</t>
+          <t>523350</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>415282</t>
+          <t>415437</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>485893</t>
+          <t>488505</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>877688</t>
+          <t>881241</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>985402</t>
+          <t>991922</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>380751</t>
+          <t>379442</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>455351</t>
+          <t>451753</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>331596</t>
+          <t>328403</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>401340</t>
+          <t>399345</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>732926</t>
+          <t>733903</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>835199</t>
+          <t>832298</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,66%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>406526</t>
+          <t>411130</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>487794</t>
+          <t>487221</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>394044</t>
+          <t>393455</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>466692</t>
+          <t>467717</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>821269</t>
+          <t>822697</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>931752</t>
+          <t>930475</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,09%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>328709</t>
+          <t>330534</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>402436</t>
+          <t>399548</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>317197</t>
+          <t>320413</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>384795</t>
+          <t>386412</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>669842</t>
+          <t>660873</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>765119</t>
+          <t>760359</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>315822</t>
+          <t>315179</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>389611</t>
+          <t>385343</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>346451</t>
+          <t>345611</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>413974</t>
+          <t>413692</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>677950</t>
+          <t>680969</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>780792</t>
+          <t>781681</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,4%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>73143</t>
+          <t>74865</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>110532</t>
+          <t>110737</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72839</t>
+          <t>72805</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>108885</t>
+          <t>107897</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>159047</t>
+          <t>158991</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>207940</t>
+          <t>211250</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,39%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>73197</t>
+          <t>72558</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>112126</t>
+          <t>111050</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>89182</t>
+          <t>87955</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>125257</t>
+          <t>125270</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>171751</t>
+          <t>171535</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>224023</t>
+          <t>226097</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,75%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>113225</t>
+          <t>112668</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>154331</t>
+          <t>154666</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>98392</t>
+          <t>97931</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>137556</t>
+          <t>137298</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>221850</t>
+          <t>221965</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>278676</t>
+          <t>282418</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>85163</t>
+          <t>84198</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>123698</t>
+          <t>121841</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>80908</t>
+          <t>81003</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>116309</t>
+          <t>116944</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>175257</t>
+          <t>175708</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>228148</t>
+          <t>230585</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,17%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>106155</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>145479</t>
+          <t>147957</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>114477</t>
+          <t>114191</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>154086</t>
+          <t>154905</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>228658</t>
+          <t>228843</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>287140</t>
+          <t>285655</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,22%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>774625</t>
+          <t>768993</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>874496</t>
+          <t>875516</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>783668</t>
+          <t>783706</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>884350</t>
+          <t>881080</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1580253</t>
+          <t>1573744</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1725407</t>
+          <t>1731194</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,25%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>589602</t>
+          <t>586729</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>679064</t>
+          <t>680472</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>594039</t>
+          <t>594084</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>685344</t>
+          <t>688409</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1208730</t>
+          <t>1202039</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1333463</t>
+          <t>1333383</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>673537</t>
+          <t>674385</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>771522</t>
+          <t>769252</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>693168</t>
+          <t>695189</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>792959</t>
+          <t>790021</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1387111</t>
+          <t>1392226</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1526549</t>
+          <t>1527024</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>559911</t>
+          <t>554681</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>649234</t>
+          <t>645777</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>589794</t>
+          <t>591679</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>679158</t>
+          <t>681933</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1173535</t>
+          <t>1174003</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1306049</t>
+          <t>1306783</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,06%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>532335</t>
+          <t>528308</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>625270</t>
+          <t>624480</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>608044</t>
+          <t>606484</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>707629</t>
+          <t>700406</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1162919</t>
+          <t>1161399</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1294819</t>
+          <t>1294429</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,88%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36B07-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36B07-Estudios-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>222333</t>
+          <t>224608</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>272175</t>
+          <t>275470</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>260610</t>
+          <t>259972</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>320143</t>
+          <t>321080</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>501007</t>
+          <t>498844</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>578890</t>
+          <t>577625</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,27%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>107998</t>
+          <t>110934</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>148086</t>
+          <t>147459</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>144451</t>
+          <t>145148</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>194776</t>
+          <t>194233</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>266345</t>
+          <t>268018</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>331222</t>
+          <t>336108</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,36%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>120165</t>
+          <t>119102</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>159754</t>
+          <t>160755</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>166374</t>
+          <t>169856</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>218591</t>
+          <t>219230</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>298632</t>
+          <t>300564</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>365622</t>
+          <t>364494</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,99%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>117115</t>
+          <t>115732</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>158157</t>
+          <t>157071</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>165273</t>
+          <t>166295</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>217021</t>
+          <t>215291</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>291920</t>
+          <t>294521</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>358483</t>
+          <t>361113</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,8%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>84143</t>
+          <t>82843</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>122946</t>
+          <t>119099</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>121114</t>
+          <t>118605</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>166330</t>
+          <t>165850</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>214289</t>
+          <t>210703</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>271612</t>
+          <t>271448</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>442411</t>
+          <t>445377</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>523350</t>
+          <t>518321</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>415437</t>
+          <t>414045</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>488505</t>
+          <t>492754</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>881241</t>
+          <t>879366</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>991922</t>
+          <t>990634</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,59%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>379442</t>
+          <t>375890</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>451753</t>
+          <t>450688</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>328403</t>
+          <t>329038</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>399345</t>
+          <t>402499</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>733903</t>
+          <t>731881</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>832298</t>
+          <t>833172</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,68%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>411130</t>
+          <t>411218</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>487221</t>
+          <t>484196</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>393455</t>
+          <t>391662</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>467717</t>
+          <t>465932</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>822697</t>
+          <t>823950</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>930475</t>
+          <t>930031</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,08%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>330534</t>
+          <t>327425</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>399548</t>
+          <t>400370</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>320413</t>
+          <t>316265</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>386412</t>
+          <t>388606</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>660873</t>
+          <t>671769</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>760359</t>
+          <t>769138</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,09%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>315179</t>
+          <t>314156</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>385343</t>
+          <t>384514</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>345611</t>
+          <t>344204</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>413692</t>
+          <t>413793</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>680969</t>
+          <t>678118</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>781681</t>
+          <t>773765</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,2%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>74865</t>
+          <t>74472</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>110737</t>
+          <t>109219</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72805</t>
+          <t>74644</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>107897</t>
+          <t>110015</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>158991</t>
+          <t>159020</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>211250</t>
+          <t>206119</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>72558</t>
+          <t>75148</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>111050</t>
+          <t>112432</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>87955</t>
+          <t>88697</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>125270</t>
+          <t>124987</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>171535</t>
+          <t>172642</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>226097</t>
+          <t>225215</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>112668</t>
+          <t>112799</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>154666</t>
+          <t>156078</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>97931</t>
+          <t>99127</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>137298</t>
+          <t>137471</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>221965</t>
+          <t>220423</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>282418</t>
+          <t>278937</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,61%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>84198</t>
+          <t>85575</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>121841</t>
+          <t>123688</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>81003</t>
+          <t>78234</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>116944</t>
+          <t>114255</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>175708</t>
+          <t>172844</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>230585</t>
+          <t>226771</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>20,82%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>106155</t>
+          <t>104887</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>147957</t>
+          <t>145996</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>114191</t>
+          <t>114360</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>154905</t>
+          <t>153898</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>228843</t>
+          <t>232057</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>285655</t>
+          <t>290212</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,64%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>768993</t>
+          <t>771424</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>875516</t>
+          <t>873926</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>783706</t>
+          <t>775843</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>881080</t>
+          <t>886505</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1573744</t>
+          <t>1577604</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1731194</t>
+          <t>1726870</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,19%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>586729</t>
+          <t>588061</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>680472</t>
+          <t>682010</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>594084</t>
+          <t>589784</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>688409</t>
+          <t>686392</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1202039</t>
+          <t>1210232</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1333383</t>
+          <t>1338157</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>674385</t>
+          <t>674865</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>769252</t>
+          <t>765383</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>695189</t>
+          <t>693719</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>790021</t>
+          <t>790745</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1392226</t>
+          <t>1397189</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1527024</t>
+          <t>1538233</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,44%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>554681</t>
+          <t>561679</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>645777</t>
+          <t>644977</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>591679</t>
+          <t>591879</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>681933</t>
+          <t>686893</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1174003</t>
+          <t>1172000</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1306783</t>
+          <t>1302970</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,01%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>528308</t>
+          <t>531058</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>624480</t>
+          <t>620171</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>606484</t>
+          <t>606856</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>700406</t>
+          <t>700315</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1161399</t>
+          <t>1167586</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1294429</t>
+          <t>1300808</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,98%</t>
         </is>
       </c>
     </row>
